--- a/Documentos Base/Sprint 1 documentacion/Sprint_01_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 1 documentacion/Sprint_01_Backlog_ICARO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 1 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343220D1-6310-4744-B10E-94251350B7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B833494-1029-48B4-A0B1-7AF9B2F541EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 01" sheetId="1" r:id="rId1"/>
@@ -120,9 +120,6 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>[Equipo]</t>
-  </si>
-  <si>
     <t>Completado</t>
   </si>
   <si>
@@ -391,6 +388,9 @@
   </si>
   <si>
     <t>34 SP / 1 semana</t>
+  </si>
+  <si>
+    <t>Isaac Sebastian Castro Muesmueran / Ivan Santiago Pulgar Leon</t>
   </si>
 </sst>
 </file>
@@ -940,7 +940,7 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
@@ -1041,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I5" s="22"/>
       <c r="J5" s="22"/>
@@ -1131,33 +1131,33 @@
         <v>3</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>31</v>
@@ -1168,34 +1168,34 @@
       <c r="G9" s="5">
         <v>5</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="J9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="L9" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>31</v>
@@ -1207,33 +1207,33 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="J10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>31</v>
@@ -1244,34 +1244,34 @@
       <c r="G11" s="5">
         <v>8</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="J11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="L11" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>31</v>
@@ -1283,33 +1283,33 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="J12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>31</v>
@@ -1320,37 +1320,37 @@
       <c r="G13" s="5">
         <v>5</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="J13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="F14" s="2">
         <v>3</v>
@@ -1359,24 +1359,24 @@
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="J14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -1424,7 +1424,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1432,21 +1432,21 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="11">
         <v>34</v>
@@ -1455,12 +1455,12 @@
         <v>34</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="14">
         <v>3</v>
@@ -1469,12 +1469,12 @@
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="11">
         <v>4</v>
@@ -1483,12 +1483,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="14">
         <v>7</v>
@@ -1497,12 +1497,12 @@
         <v>7</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="11">
         <v>7</v>
@@ -1511,12 +1511,12 @@
         <v>7</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="14">
         <v>0</v>
@@ -1525,12 +1525,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="11">
         <v>0</v>
@@ -1539,12 +1539,12 @@
         <v>0</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="14">
         <v>17</v>
@@ -1553,26 +1553,26 @@
         <v>17</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>96</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="14">
         <v>15</v>
@@ -1581,21 +1581,21 @@
         <v>15</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>100</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1617,26 +1617,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
         <v>102</v>
-      </c>
-      <c r="B1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
         <v>104</v>
-      </c>
-      <c r="B2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1644,63 +1644,63 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" t="s">
         <v>108</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
         <v>110</v>
-      </c>
-      <c r="B6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" t="s">
         <v>112</v>
-      </c>
-      <c r="B7" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
         <v>114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
         <v>116</v>
-      </c>
-      <c r="B9" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
         <v>118</v>
-      </c>
-      <c r="B10" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Documentos Base/Sprint 1 documentacion/Sprint_01_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 1 documentacion/Sprint_01_Backlog_ICARO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 1 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B833494-1029-48B4-A0B1-7AF9B2F541EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B583D3D4-2838-42ED-BB0E-FA670190CFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,13 +16,14 @@
     <sheet name="Backlog Sprint 01" sheetId="1" r:id="rId1"/>
     <sheet name="Resumen Velocidad" sheetId="2" r:id="rId2"/>
     <sheet name="Glosario" sheetId="3" r:id="rId3"/>
+    <sheet name="Resumen de Casos de Prueba " sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="211">
   <si>
     <t>SPRINT BACKLOG — Sprint 01: Infraestructura Base, Autenticación y Gestión de Usuarios</t>
   </si>
@@ -333,54 +334,24 @@
     <t>Significado</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>Actividad de Montaje — tarea de infraestructura/arquitectura base</t>
-  </si>
-  <si>
-    <t>Historia de Usuario — funcionalidad desde la perspectiva del usuario</t>
-  </si>
-  <si>
-    <t>Historia Técnica — tarea técnica transversal</t>
-  </si>
-  <si>
     <t>SP</t>
   </si>
   <si>
-    <t>Story Point — unidad de estimación de esfuerzo en Scrum</t>
-  </si>
-  <si>
     <t>RBAC</t>
   </si>
   <si>
-    <t>Role-Based Access Control — control de acceso basado en roles</t>
-  </si>
-  <si>
     <t>JWT</t>
   </si>
   <si>
-    <t>JSON Web Token — estándar de autenticación firmado digitalmente</t>
-  </si>
-  <si>
     <t>ORM</t>
   </si>
   <si>
-    <t>Object-Relational Mapper — herramienta de mapeo objeto-relacional (Prisma)</t>
-  </si>
-  <si>
     <t>CRUD</t>
   </si>
   <si>
-    <t>Create, Read, Update, Delete — operaciones básicas sobre datos</t>
-  </si>
-  <si>
     <t>DoD</t>
   </si>
   <si>
-    <t>Definition of Done — criterios que definen un ítem como completado</t>
-  </si>
-  <si>
     <t>BD</t>
   </si>
   <si>
@@ -391,13 +362,307 @@
   </si>
   <si>
     <t>Isaac Sebastian Castro Muesmueran / Ivan Santiago Pulgar Leon</t>
+  </si>
+  <si>
+    <t>GLOSARIO DE SIGLAS</t>
+  </si>
+  <si>
+    <t>Contexto de uso</t>
+  </si>
+  <si>
+    <t>Historia de Usuario</t>
+  </si>
+  <si>
+    <t>Tipo de ítem del backlog orientado a funcionalidad</t>
+  </si>
+  <si>
+    <t>Historia Técnica</t>
+  </si>
+  <si>
+    <t>Tarea técnica transversal del equipo</t>
+  </si>
+  <si>
+    <t>Story Point</t>
+  </si>
+  <si>
+    <t>Unidad relativa de estimación de esfuerzo</t>
+  </si>
+  <si>
+    <t>Role-Based Access Control</t>
+  </si>
+  <si>
+    <t>Control de acceso basado en roles</t>
+  </si>
+  <si>
+    <t>JSON Web Token</t>
+  </si>
+  <si>
+    <t>Estándar de autenticación firmado digitalmente</t>
+  </si>
+  <si>
+    <t>Create, Read, Update, Delete</t>
+  </si>
+  <si>
+    <t>Operaciones básicas de gestión</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Application Programming Interface</t>
+  </si>
+  <si>
+    <t>Interfaz de programación entre componentes</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>Portable Document Format</t>
+  </si>
+  <si>
+    <t>Formato de salida de la planilla mensual de obra</t>
+  </si>
+  <si>
+    <t>Definition of Done</t>
+  </si>
+  <si>
+    <t>Criterios que definen un ítem como completado</t>
+  </si>
+  <si>
+    <t>Object-Relational Mapper</t>
+  </si>
+  <si>
+    <t>Herramienta de mapeo objeto-relacional (Prisma)</t>
+  </si>
+  <si>
+    <t>Repositorio estructurado de datos del sistema</t>
+  </si>
+  <si>
+    <t>BCK</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Prefijo del código documental del backlog</t>
+  </si>
+  <si>
+    <t>SPR</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Iteración de desarrollo en metodología Scrum</t>
+  </si>
+  <si>
+    <t>PLN-REA</t>
+  </si>
+  <si>
+    <t>Planificado-Realizado</t>
+  </si>
+  <si>
+    <t>Documento de comparación de sprint</t>
+  </si>
+  <si>
+    <t>INF-PRU</t>
+  </si>
+  <si>
+    <t>Informe de Pruebas</t>
+  </si>
+  <si>
+    <t>Documento de resultados de pruebas del sprint</t>
+  </si>
+  <si>
+    <t>ID CP</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Evidencia</t>
+  </si>
+  <si>
+    <t>Grupo 1</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Grupo 2</t>
+  </si>
+  <si>
+    <t>Grupo 3</t>
+  </si>
+  <si>
+    <t>Grupo 4</t>
+  </si>
+  <si>
+    <t>CP-001</t>
+  </si>
+  <si>
+    <t>Autenticación / JWT</t>
+  </si>
+  <si>
+    <t>Sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 01</t>
+  </si>
+  <si>
+    <t>CP-002</t>
+  </si>
+  <si>
+    <t>Token con formato inválido, sin Bearer → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 02</t>
+  </si>
+  <si>
+    <t>CP-003</t>
+  </si>
+  <si>
+    <t>Token firmado con secreto incorrecto → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 03</t>
+  </si>
+  <si>
+    <t>CP-004</t>
+  </si>
+  <si>
+    <t>Token expirado → 401 con mensaje de sesión expirada</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 04</t>
+  </si>
+  <si>
+    <t>CP-005</t>
+  </si>
+  <si>
+    <t>Token válido de Admin → pasa autenticación y retorna 200 o 404 controlado</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 05</t>
+  </si>
+  <si>
+    <t>CP-006</t>
+  </si>
+  <si>
+    <t>Usuarios / RBAC</t>
+  </si>
+  <si>
+    <t>GET /users sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 06</t>
+  </si>
+  <si>
+    <t>CP-007</t>
+  </si>
+  <si>
+    <t>GET /users con rol Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 07</t>
+  </si>
+  <si>
+    <t>CP-008</t>
+  </si>
+  <si>
+    <t>GET /users con rol Contador → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 08</t>
+  </si>
+  <si>
+    <t>CP-009</t>
+  </si>
+  <si>
+    <t>GET /users con token Admin → pasa RBAC</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 09</t>
+  </si>
+  <si>
+    <t>CP-010</t>
+  </si>
+  <si>
+    <t>POST /users con rol Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 10</t>
+  </si>
+  <si>
+    <t>CP-011</t>
+  </si>
+  <si>
+    <t>PATCH /users/:id/role con rol Contador → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 11</t>
+  </si>
+  <si>
+    <t>CP-012</t>
+  </si>
+  <si>
+    <t>Login / Rutas Públicas</t>
+  </si>
+  <si>
+    <t>POST /auth/login sin token → ruta accesible y valida campos obligatorios</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 12</t>
+  </si>
+  <si>
+    <t>CP-013</t>
+  </si>
+  <si>
+    <t>Health Check</t>
+  </si>
+  <si>
+    <t>GET /health → 200 sin autenticación</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 13</t>
+  </si>
+  <si>
+    <t>CP-014</t>
+  </si>
+  <si>
+    <t>Proyectos / Acceso</t>
+  </si>
+  <si>
+    <t>GET /proyectos/:id sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 14</t>
+  </si>
+  <si>
+    <t>CP-015</t>
+  </si>
+  <si>
+    <t>Proyectos / Acceso por Proyecto</t>
+  </si>
+  <si>
+    <t>GET /proyectos/:id con token Residente sin asignación en BD → 403 o 500 controlado</t>
+  </si>
+  <si>
+    <t>security.test.js – Test</t>
+  </si>
+  <si>
+    <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 01 (CP-001 a CP-015)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,38 +675,45 @@
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -452,6 +724,34 @@
     <font>
       <i/>
       <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -494,7 +794,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -541,11 +841,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -620,6 +950,51 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,17 +1011,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35BF6D30-7B24-4626-AA87-82DFBE8EC22A}" name="Tabla2" displayName="Tabla2" ref="A1:B11" totalsRowShown="0">
-  <autoFilter ref="A1:B11" xr:uid="{35BF6D30-7B24-4626-AA87-82DFBE8EC22A}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{02D9E4F1-842F-4A39-A4B8-EE484781FC9F}" name="Sigla"/>
-    <tableColumn id="2" xr3:uid="{E1E312E9-1AFA-41A7-AEF7-E08CA7A3867F}" name="Significado"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -938,11 +1302,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="7" width="9" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="40" customWidth="1"/>
@@ -1026,7 +1391,7 @@
       <c r="K4" s="25"/>
       <c r="L4" s="26"/>
     </row>
-    <row r="5" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>8</v>
       </c>
@@ -1041,7 +1406,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I5" s="22"/>
       <c r="J5" s="22"/>
@@ -1131,7 +1496,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>32</v>
@@ -1169,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>32</v>
@@ -1207,7 +1572,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>32</v>
@@ -1245,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>32</v>
@@ -1283,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>32</v>
@@ -1321,7 +1686,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>32</v>
@@ -1359,7 +1724,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>32</v>
@@ -1553,7 +1918,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1608,130 +1973,649 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763E11AF-F722-4524-841D-EB284C50087B}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="72.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" s="30" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" s="30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B6" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B12" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B13" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="C13" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>149</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B11">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1898C963-16D1-41BA-A783-154B1ABEC1D5}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="75.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Documentos Base/Sprint 1 documentacion/Sprint_01_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 1 documentacion/Sprint_01_Backlog_ICARO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 1 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B583D3D4-2838-42ED-BB0E-FA670190CFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B279D708-B4C9-4561-8E28-25A4FAE02988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 01" sheetId="1" r:id="rId1"/>
@@ -652,10 +652,10 @@
     <t>GET /proyectos/:id con token Residente sin asignación en BD → 403 o 500 controlado</t>
   </si>
   <si>
-    <t>security.test.js – Test</t>
-  </si>
-  <si>
     <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 01 (CP-001 a CP-015)</t>
+  </si>
+  <si>
+    <t>security.test.js – Test 15</t>
   </si>
 </sst>
 </file>
@@ -875,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -899,28 +899,46 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -948,53 +966,36 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1316,124 +1317,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="16" t="s">
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="29"/>
     </row>
     <row r="4" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="30">
         <v>46125</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="16" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="30">
         <v>46129</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="26"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="32"/>
     </row>
     <row r="5" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="16" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="23"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="29"/>
     </row>
     <row r="6" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="16" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="23"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="29"/>
     </row>
     <row r="7" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1740,13 +1741,13 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="8">
         <v>34</v>
       </c>
@@ -1788,178 +1789,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="38" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="40">
         <v>34</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="40">
         <v>34</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="43">
         <v>3</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="43">
         <v>3</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="44" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="40">
         <v>4</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="40">
         <v>4</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="41" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="43">
         <v>7</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="43">
         <v>7</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="44" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="40">
         <v>7</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="40">
         <v>7</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="41" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="43">
         <v>0</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="43">
         <v>0</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="44" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="40">
         <v>0</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="40">
         <v>0</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="41" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="43">
         <v>17</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="43">
         <v>17</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="44" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="41" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="43">
         <v>15</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="43">
         <v>15</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="44" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="41" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1982,185 +1983,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="12" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="14" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="14" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="12" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="14" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="12" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="14" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="14" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="12" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="14" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="12" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2188,429 +2189,429 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
-        <v>194</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="B16" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F16" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="B17" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
